--- a/data/trans_dic/Q20C_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/Q20C_R2-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con mayor tiempo de espera (más de 7 meses) para ser hopitalizado</t>
+          <t>Población con mayor tiempo de espera (más de 7 meses) para ser hopitalizado (tasa de respuesta: 95,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,99; 58,81</t>
+          <t>16,1; 58,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,01; 38,26</t>
+          <t>7,42; 40,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,26</t>
+          <t>0,0; 39,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,31; 56,94</t>
+          <t>16,03; 56,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,4; 44,27</t>
+          <t>12,13; 41,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,66; 38,18</t>
+          <t>10,74; 37,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,87; 37,8</t>
+          <t>6,71; 38,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 25,37</t>
+          <t>2,47; 27,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,93; 43,64</t>
+          <t>17,41; 41,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,7; 31,33</t>
+          <t>11,07; 32,69</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,55; 30,61</t>
+          <t>5,21; 29,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,32; 38,74</t>
+          <t>12,82; 36,84</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,69; 39,86</t>
+          <t>7,92; 39,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,71; 49,62</t>
+          <t>15,23; 49,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,0; 40,27</t>
+          <t>9,26; 38,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,39</t>
+          <t>0,0; 28,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,28; 45,3</t>
+          <t>12,64; 46,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,19; 50,92</t>
+          <t>18,96; 52,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,52; 36,76</t>
+          <t>9,93; 37,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,63</t>
+          <t>0,0; 21,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,71; 38,41</t>
+          <t>13,85; 37,78</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,52; 43,93</t>
+          <t>20,42; 45,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,18; 33,48</t>
+          <t>13,96; 33,68</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,92</t>
+          <t>0,0; 70,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,89</t>
+          <t>0,0; 53,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,02; 86,72</t>
+          <t>13,8; 86,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,76; 60,99</t>
+          <t>5,48; 57,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,22</t>
+          <t>0,0; 58,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,19; 70,86</t>
+          <t>9,59; 70,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,68; 45,71</t>
+          <t>9,23; 44,86</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,05; 43,79</t>
+          <t>13,46; 42,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,91; 32,0</t>
+          <t>10,38; 33,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,87; 38,72</t>
+          <t>11,27; 35,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,12; 40,07</t>
+          <t>16,52; 38,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,14; 30,04</t>
+          <t>9,32; 30,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,96; 37,77</t>
+          <t>17,77; 37,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,52; 39,48</t>
+          <t>15,44; 38,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,02; 29,08</t>
+          <t>11,15; 29,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,61; 30,44</t>
+          <t>13,58; 31,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,4; 32,13</t>
+          <t>17,1; 31,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,72; 33,58</t>
+          <t>17,33; 34,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,21; 30,59</t>
+          <t>16,21; 31,02</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con mayor tiempo de espera (más de 7 meses) para ser hopitalizado</t>
+          <t>Población con mayor tiempo de espera (más de 7 meses) para ser hopitalizado (tasa de respuesta: 95,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2754; 10128</t>
+          <t>2774; 10098</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1950; 10645</t>
+          <t>2064; 11388</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4425</t>
+          <t>0; 5120</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2524; 8812</t>
+          <t>2480; 8766</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3801; 13577</t>
+          <t>3719; 12850</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4068; 14574</t>
+          <t>4099; 14275</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1704; 9382</t>
+          <t>1665; 9430</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>331; 3272</t>
+          <t>318; 3510</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8587; 20901</t>
+          <t>8338; 19891</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7062; 20673</t>
+          <t>7303; 21575</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2095; 11552</t>
+          <t>1965; 11126</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3781; 10992</t>
+          <t>3638; 10451</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1601</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2164; 11217</t>
+          <t>2230; 11204</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5345; 16883</t>
+          <t>5182; 16904</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3053; 12300</t>
+          <t>2827; 11830</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4041</t>
+          <t>0; 4056</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4168; 15383</t>
+          <t>4292; 15818</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5410; 17013</t>
+          <t>6337; 17424</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2280; 8806</t>
+          <t>2378; 8943</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4966</t>
+          <t>0; 4776</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9132; 23850</t>
+          <t>8600; 23460</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13837; 29628</t>
+          <t>13768; 30593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7184; 18247</t>
+          <t>7605; 18356</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6106</t>
+          <t>0; 5904</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1760</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1572</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 6094</t>
+          <t>0; 5700</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1491</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1267; 7834</t>
+          <t>1247; 7827</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1148</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>471; 4247</t>
+          <t>382; 3974</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 7020</t>
+          <t>0; 7294</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1114; 8592</t>
+          <t>1162; 8516</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 1678</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1535; 8080</t>
+          <t>1632; 7930</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4680; 14587</t>
+          <t>4484; 14136</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6444; 18900</t>
+          <t>6131; 19556</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6087; 19857</t>
+          <t>5778; 18392</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9714; 22730</t>
+          <t>9372; 21865</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3990; 14723</t>
+          <t>4570; 14833</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14580; 30653</t>
+          <t>14419; 30731</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9952; 23784</t>
+          <t>9300; 23282</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5266; 12741</t>
+          <t>4885; 12820</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11208; 25061</t>
+          <t>11181; 26193</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24401; 45049</t>
+          <t>23980; 43981</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18642; 37453</t>
+          <t>19332; 38315</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16301; 30760</t>
+          <t>16303; 31186</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Q20C_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/Q20C_R2-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,1; 58,64</t>
+          <t>16,25; 62,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,42; 40,93</t>
+          <t>6,87; 37,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,64</t>
+          <t>0,0; 40,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,03; 56,64</t>
+          <t>16,09; 57,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,13; 41,9</t>
+          <t>12,2; 41,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,74; 37,4</t>
+          <t>10,4; 36,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,71; 38,0</t>
+          <t>7,11; 39,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 27,21</t>
+          <t>2,43; 26,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,41; 41,54</t>
+          <t>17,55; 43,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,07; 32,69</t>
+          <t>12,28; 32,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,21; 29,48</t>
+          <t>5,24; 30,76</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,82; 36,84</t>
+          <t>12,03; 36,98</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>26,14%</t>
         </is>
       </c>
     </row>
@@ -862,57 +862,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,92; 39,82</t>
+          <t>9,96; 40,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,23; 49,68</t>
+          <t>14,81; 50,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,26; 38,73</t>
+          <t>14,33; 44,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,5</t>
+          <t>0,0; 32,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,64; 46,58</t>
+          <t>12,31; 44,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,96; 52,15</t>
+          <t>18,28; 54,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,93; 37,34</t>
+          <t>12,43; 41,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,76</t>
+          <t>0,0; 22,23</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,85; 37,78</t>
+          <t>14,01; 36,14</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,42; 45,36</t>
+          <t>21,17; 44,83</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,96; 33,68</t>
+          <t>16,97; 37,17</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,51</t>
+          <t>0,0; 72,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,21</t>
+          <t>5,62; 52,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,8; 86,64</t>
+          <t>13,09; 84,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,48; 57,07</t>
+          <t>7,97; 59,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,4</t>
+          <t>0,0; 52,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,59; 70,23</t>
+          <t>8,47; 71,5</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,23; 44,86</t>
+          <t>11,05; 46,23</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,46; 42,44</t>
+          <t>13,49; 44,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,38; 33,11</t>
+          <t>10,75; 31,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,27; 35,87</t>
+          <t>11,01; 35,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,52; 38,54</t>
+          <t>18,9; 40,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,32; 30,26</t>
+          <t>8,32; 30,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,77; 37,86</t>
+          <t>17,42; 37,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,44; 38,64</t>
+          <t>16,25; 39,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,15; 29,26</t>
+          <t>12,44; 29,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,58; 31,82</t>
+          <t>13,24; 31,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,1; 31,37</t>
+          <t>17,03; 31,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,33; 34,35</t>
+          <t>17,23; 33,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,21; 31,02</t>
+          <t>17,71; 32,3</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>6867</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2774; 10098</t>
+          <t>2798; 10749</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2064; 11388</t>
+          <t>1911; 10488</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5120</t>
+          <t>0; 5295</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2480; 8766</t>
+          <t>2569; 9140</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3719; 12850</t>
+          <t>3741; 12768</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4099; 14275</t>
+          <t>3968; 14072</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1665; 9430</t>
+          <t>1766; 9854</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>318; 3510</t>
+          <t>352; 3776</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8338; 19891</t>
+          <t>8402; 20616</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7303; 21575</t>
+          <t>8101; 21296</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1965; 11126</t>
+          <t>1976; 11609</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3638; 10451</t>
+          <t>3666; 11269</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>16391</t>
         </is>
       </c>
     </row>
@@ -1717,57 +1717,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2230; 11204</t>
+          <t>2802; 11421</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5182; 16904</t>
+          <t>5039; 17108</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2827; 11830</t>
+          <t>5072; 15767</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4056</t>
+          <t>0; 4670</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4292; 15818</t>
+          <t>4181; 15155</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6337; 17424</t>
+          <t>6109; 18053</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2378; 8943</t>
+          <t>3394; 11303</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4776</t>
+          <t>0; 4878</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8600; 23460</t>
+          <t>8702; 22441</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13768; 30593</t>
+          <t>14277; 30235</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7605; 18356</t>
+          <t>10639; 23311</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4788</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5904</t>
+          <t>0; 6068</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5700</t>
+          <t>629; 5896</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1247; 7827</t>
+          <t>1183; 7674</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1955,17 +1955,17 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>382; 3974</t>
+          <t>685; 5093</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 7294</t>
+          <t>0; 6527</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1162; 8516</t>
+          <t>1027; 8670</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1632; 7930</t>
+          <t>2187; 9146</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14839</t>
+          <t>17774</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>10272</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23127</t>
+          <t>28046</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4484; 14136</t>
+          <t>4492; 14910</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6131; 19556</t>
+          <t>6350; 18818</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5778; 18392</t>
+          <t>5647; 18297</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9372; 21865</t>
+          <t>11824; 25634</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4570; 14833</t>
+          <t>4076; 14980</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14419; 30731</t>
+          <t>14137; 30575</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9300; 23282</t>
+          <t>9792; 23513</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4885; 12820</t>
+          <t>6272; 14935</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11181; 26193</t>
+          <t>10902; 25698</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23980; 43981</t>
+          <t>23883; 44615</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19332; 38315</t>
+          <t>19221; 37717</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16303; 31186</t>
+          <t>20005; 36486</t>
         </is>
       </c>
     </row>
